--- a/mapping/SB_DWH/Mapping_DIM_LOS_GEO.xlsx
+++ b/mapping/SB_DWH/Mapping_DIM_LOS_GEO.xlsx
@@ -881,7 +881,11 @@
           <t>VARCHAR2</t>
         </is>
       </c>
-      <c r="C9" s="31" t="inlineStr"/>
+      <c r="C9" s="31" t="inlineStr">
+        <is>
+          <t>Mã tỉnh thành</t>
+        </is>
+      </c>
       <c r="D9" s="17" t="inlineStr"/>
       <c r="E9" s="17" t="inlineStr">
         <is>
@@ -933,7 +937,11 @@
           <t>VARCHAR2</t>
         </is>
       </c>
-      <c r="C11" s="31" t="inlineStr"/>
+      <c r="C11" s="31" t="inlineStr">
+        <is>
+          <t>Tên tỉnh thành (có dấu)</t>
+        </is>
+      </c>
       <c r="D11" s="17" t="inlineStr"/>
       <c r="E11" s="17" t="inlineStr">
         <is>
@@ -957,7 +965,11 @@
           <t>VARCHAR2</t>
         </is>
       </c>
-      <c r="C12" s="31" t="inlineStr"/>
+      <c r="C12" s="31" t="inlineStr">
+        <is>
+          <t>Mã quận huyện</t>
+        </is>
+      </c>
       <c r="D12" s="17" t="inlineStr"/>
       <c r="E12" s="17" t="inlineStr">
         <is>
@@ -1009,7 +1021,11 @@
           <t>VARCHAR2</t>
         </is>
       </c>
-      <c r="C14" s="31" t="inlineStr"/>
+      <c r="C14" s="31" t="inlineStr">
+        <is>
+          <t>Tên quận huyện (có dấu)</t>
+        </is>
+      </c>
       <c r="D14" s="17" t="inlineStr">
         <is>
           <t>Làm sạch giá trị lỗi #NA và #REF! còn sót từ import Excel</t>
@@ -1037,7 +1053,11 @@
           <t>DATE</t>
         </is>
       </c>
-      <c r="C15" s="31" t="inlineStr"/>
+      <c r="C15" s="31" t="inlineStr">
+        <is>
+          <t>Ngày bắt đầu hiệu lực</t>
+        </is>
+      </c>
       <c r="D15" s="17" t="inlineStr"/>
       <c r="E15" s="17" t="inlineStr">
         <is>
@@ -1061,7 +1081,11 @@
           <t>DATE</t>
         </is>
       </c>
-      <c r="C16" s="31" t="inlineStr"/>
+      <c r="C16" s="31" t="inlineStr">
+        <is>
+          <t>Ngày hết hiệu lực</t>
+        </is>
+      </c>
       <c r="D16" s="17" t="inlineStr"/>
       <c r="E16" s="17" t="inlineStr">
         <is>
